--- a/artfynd/A 58197-2023 artfynd.xlsx
+++ b/artfynd/A 58197-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120168834</v>
+        <v>120168837</v>
       </c>
       <c r="B2" t="n">
         <v>57310</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>512698</v>
+        <v>512736</v>
       </c>
       <c r="R2" t="n">
-        <v>7087939</v>
+        <v>7087924</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120168845</v>
+        <v>120168841</v>
       </c>
       <c r="B3" t="n">
-        <v>57326</v>
+        <v>57310</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,16 +798,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>512559</v>
+        <v>512591</v>
       </c>
       <c r="R3" t="n">
-        <v>7087832</v>
+        <v>7087881</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack ganska färska</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120168847</v>
+        <v>120168844</v>
       </c>
       <c r="B4" t="n">
-        <v>78526</v>
+        <v>57326</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512728</v>
+        <v>512743</v>
       </c>
       <c r="R4" t="n">
-        <v>7087945</v>
+        <v>7087946</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,6 +965,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120168836</v>
+        <v>120168834</v>
       </c>
       <c r="B5" t="n">
         <v>57310</v>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>512738</v>
+        <v>512698</v>
       </c>
       <c r="R5" t="n">
-        <v>7087943</v>
+        <v>7087939</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120168813</v>
+        <v>120168847</v>
       </c>
       <c r="B6" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>512641</v>
+        <v>512728</v>
       </c>
       <c r="R6" t="n">
-        <v>7087947</v>
+        <v>7087945</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120168835</v>
+        <v>120168840</v>
       </c>
       <c r="B7" t="n">
         <v>57310</v>
@@ -1240,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>512748</v>
+        <v>512707</v>
       </c>
       <c r="R7" t="n">
-        <v>7087939</v>
+        <v>7087909</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1285,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120168839</v>
+        <v>120168842</v>
       </c>
       <c r="B8" t="n">
         <v>57310</v>
@@ -1347,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>512725</v>
+        <v>512537</v>
       </c>
       <c r="R8" t="n">
-        <v>7087919</v>
+        <v>7087781</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1392,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,7 +1419,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120168842</v>
+        <v>120168836</v>
       </c>
       <c r="B9" t="n">
         <v>57310</v>
@@ -1454,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>512537</v>
+        <v>512738</v>
       </c>
       <c r="R9" t="n">
-        <v>7087781</v>
+        <v>7087943</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1499,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,7 +1526,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120168841</v>
+        <v>120168839</v>
       </c>
       <c r="B10" t="n">
         <v>57310</v>
@@ -1561,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>512591</v>
+        <v>512725</v>
       </c>
       <c r="R10" t="n">
-        <v>7087881</v>
+        <v>7087919</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1606,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack ganska färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120168840</v>
+        <v>120168813</v>
       </c>
       <c r="B11" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1644,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1668,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>512707</v>
+        <v>512641</v>
       </c>
       <c r="R11" t="n">
-        <v>7087909</v>
+        <v>7087947</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1704,11 +1709,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1842,10 +1842,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120168844</v>
+        <v>120168835</v>
       </c>
       <c r="B13" t="n">
-        <v>57326</v>
+        <v>57310</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1858,16 +1858,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>512743</v>
+        <v>512748</v>
       </c>
       <c r="R13" t="n">
-        <v>7087946</v>
+        <v>7087939</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120168837</v>
+        <v>120168845</v>
       </c>
       <c r="B14" t="n">
-        <v>57310</v>
+        <v>57326</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1965,16 +1965,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>512736</v>
+        <v>512559</v>
       </c>
       <c r="R14" t="n">
-        <v>7087924</v>
+        <v>7087832</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 58197-2023 artfynd.xlsx
+++ b/artfynd/A 58197-2023 artfynd.xlsx
@@ -1526,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120168839</v>
+        <v>120168813</v>
       </c>
       <c r="B10" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1542,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>512725</v>
+        <v>512641</v>
       </c>
       <c r="R10" t="n">
-        <v>7087919</v>
+        <v>7087947</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,11 +1602,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120168813</v>
+        <v>120168839</v>
       </c>
       <c r="B11" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1649,21 +1644,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>512641</v>
+        <v>512725</v>
       </c>
       <c r="R11" t="n">
-        <v>7087947</v>
+        <v>7087919</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,6 +1704,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 58197-2023 artfynd.xlsx
+++ b/artfynd/A 58197-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120168837</v>
+        <v>120168844</v>
       </c>
       <c r="B2" t="n">
-        <v>57310</v>
+        <v>57326</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>512736</v>
+        <v>512743</v>
       </c>
       <c r="R2" t="n">
-        <v>7087924</v>
+        <v>7087946</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120168844</v>
+        <v>120168839</v>
       </c>
       <c r="B4" t="n">
-        <v>57326</v>
+        <v>57310</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,16 +905,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512743</v>
+        <v>512725</v>
       </c>
       <c r="R4" t="n">
-        <v>7087946</v>
+        <v>7087919</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120168834</v>
+        <v>120168838</v>
       </c>
       <c r="B5" t="n">
         <v>57310</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>512698</v>
+        <v>512730</v>
       </c>
       <c r="R5" t="n">
-        <v>7087939</v>
+        <v>7087928</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120168847</v>
+        <v>120168835</v>
       </c>
       <c r="B6" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>512728</v>
+        <v>512748</v>
       </c>
       <c r="R6" t="n">
-        <v>7087945</v>
+        <v>7087939</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,6 +1179,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120168840</v>
+        <v>120168845</v>
       </c>
       <c r="B7" t="n">
-        <v>57310</v>
+        <v>57326</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,16 +1226,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1245,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>512707</v>
+        <v>512559</v>
       </c>
       <c r="R7" t="n">
-        <v>7087909</v>
+        <v>7087832</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120168842</v>
+        <v>120168847</v>
       </c>
       <c r="B8" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,21 +1333,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>512537</v>
+        <v>512728</v>
       </c>
       <c r="R8" t="n">
-        <v>7087781</v>
+        <v>7087945</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,11 +1393,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1526,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120168813</v>
+        <v>120168842</v>
       </c>
       <c r="B10" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1542,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>512641</v>
+        <v>512537</v>
       </c>
       <c r="R10" t="n">
-        <v>7087947</v>
+        <v>7087781</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,6 +1602,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120168839</v>
+        <v>120168813</v>
       </c>
       <c r="B11" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1644,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1668,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>512725</v>
+        <v>512641</v>
       </c>
       <c r="R11" t="n">
-        <v>7087919</v>
+        <v>7087947</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1704,11 +1709,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,7 +1735,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120168838</v>
+        <v>120168834</v>
       </c>
       <c r="B12" t="n">
         <v>57310</v>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>512730</v>
+        <v>512698</v>
       </c>
       <c r="R12" t="n">
-        <v>7087928</v>
+        <v>7087939</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1842,7 +1842,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120168835</v>
+        <v>120168837</v>
       </c>
       <c r="B13" t="n">
         <v>57310</v>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>512748</v>
+        <v>512736</v>
       </c>
       <c r="R13" t="n">
-        <v>7087939</v>
+        <v>7087924</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120168845</v>
+        <v>120168840</v>
       </c>
       <c r="B14" t="n">
-        <v>57326</v>
+        <v>57310</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1965,16 +1965,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>512559</v>
+        <v>512707</v>
       </c>
       <c r="R14" t="n">
-        <v>7087832</v>
+        <v>7087909</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 58197-2023 artfynd.xlsx
+++ b/artfynd/A 58197-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120168844</v>
+        <v>120168838</v>
       </c>
       <c r="B2" t="n">
-        <v>57326</v>
+        <v>57320</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>512743</v>
+        <v>512730</v>
       </c>
       <c r="R2" t="n">
-        <v>7087946</v>
+        <v>7087928</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120168841</v>
+        <v>120168835</v>
       </c>
       <c r="B3" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>512591</v>
+        <v>512748</v>
       </c>
       <c r="R3" t="n">
-        <v>7087881</v>
+        <v>7087939</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack ganska färska</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120168839</v>
+        <v>120168813</v>
       </c>
       <c r="B4" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512725</v>
+        <v>512641</v>
       </c>
       <c r="R4" t="n">
-        <v>7087919</v>
+        <v>7087947</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120168838</v>
+        <v>120168841</v>
       </c>
       <c r="B5" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>512730</v>
+        <v>512591</v>
       </c>
       <c r="R5" t="n">
-        <v>7087928</v>
+        <v>7087881</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1071,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack ganska färska</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120168835</v>
+        <v>120168837</v>
       </c>
       <c r="B6" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>512748</v>
+        <v>512736</v>
       </c>
       <c r="R6" t="n">
-        <v>7087939</v>
+        <v>7087924</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1213,7 +1208,7 @@
         <v>120168845</v>
       </c>
       <c r="B7" t="n">
-        <v>57326</v>
+        <v>57336</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1317,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120168847</v>
+        <v>120168844</v>
       </c>
       <c r="B8" t="n">
-        <v>78526</v>
+        <v>57336</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1357,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>512728</v>
+        <v>512743</v>
       </c>
       <c r="R8" t="n">
-        <v>7087945</v>
+        <v>7087946</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1393,6 +1388,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120168836</v>
+        <v>120168839</v>
       </c>
       <c r="B9" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>512738</v>
+        <v>512725</v>
       </c>
       <c r="R9" t="n">
-        <v>7087943</v>
+        <v>7087919</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1526,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120168842</v>
+        <v>120168840</v>
       </c>
       <c r="B10" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>512537</v>
+        <v>512707</v>
       </c>
       <c r="R10" t="n">
-        <v>7087781</v>
+        <v>7087909</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120168813</v>
+        <v>120168842</v>
       </c>
       <c r="B11" t="n">
-        <v>90562</v>
+        <v>57320</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1649,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>512641</v>
+        <v>512537</v>
       </c>
       <c r="R11" t="n">
-        <v>7087947</v>
+        <v>7087781</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,6 +1709,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120168834</v>
+        <v>120168836</v>
       </c>
       <c r="B12" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1775,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>512698</v>
+        <v>512738</v>
       </c>
       <c r="R12" t="n">
-        <v>7087939</v>
+        <v>7087943</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1820,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1842,10 +1847,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120168837</v>
+        <v>120168847</v>
       </c>
       <c r="B13" t="n">
-        <v>57310</v>
+        <v>78542</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1858,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1882,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>512736</v>
+        <v>512728</v>
       </c>
       <c r="R13" t="n">
-        <v>7087924</v>
+        <v>7087945</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1918,11 +1923,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120168840</v>
+        <v>120168834</v>
       </c>
       <c r="B14" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>512707</v>
+        <v>512698</v>
       </c>
       <c r="R14" t="n">
-        <v>7087909</v>
+        <v>7087939</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 58197-2023 artfynd.xlsx
+++ b/artfynd/A 58197-2023 artfynd.xlsx
@@ -1633,7 +1633,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120168842</v>
+        <v>120168836</v>
       </c>
       <c r="B11" t="n">
         <v>57320</v>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>512537</v>
+        <v>512738</v>
       </c>
       <c r="R11" t="n">
-        <v>7087781</v>
+        <v>7087943</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1713,7 +1713,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1740,7 +1740,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120168836</v>
+        <v>120168842</v>
       </c>
       <c r="B12" t="n">
         <v>57320</v>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>512738</v>
+        <v>512537</v>
       </c>
       <c r="R12" t="n">
-        <v>7087943</v>
+        <v>7087781</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 58197-2023 artfynd.xlsx
+++ b/artfynd/A 58197-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120168838</v>
+        <v>120168845</v>
       </c>
       <c r="B2" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>512730</v>
+        <v>512559</v>
       </c>
       <c r="R2" t="n">
-        <v>7087928</v>
+        <v>7087832</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120168835</v>
+        <v>120168839</v>
       </c>
       <c r="B3" t="n">
         <v>57320</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>512748</v>
+        <v>512725</v>
       </c>
       <c r="R3" t="n">
-        <v>7087939</v>
+        <v>7087919</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120168813</v>
+        <v>120168836</v>
       </c>
       <c r="B4" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512641</v>
+        <v>512738</v>
       </c>
       <c r="R4" t="n">
-        <v>7087947</v>
+        <v>7087943</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,6 +965,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120168841</v>
+        <v>120168838</v>
       </c>
       <c r="B5" t="n">
         <v>57320</v>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>512591</v>
+        <v>512730</v>
       </c>
       <c r="R5" t="n">
-        <v>7087881</v>
+        <v>7087928</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack ganska färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1205,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120168845</v>
+        <v>120168835</v>
       </c>
       <c r="B7" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,16 +1226,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1245,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>512559</v>
+        <v>512748</v>
       </c>
       <c r="R7" t="n">
-        <v>7087832</v>
+        <v>7087939</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120168844</v>
+        <v>120168847</v>
       </c>
       <c r="B8" t="n">
-        <v>57336</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,21 +1333,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>512743</v>
+        <v>512728</v>
       </c>
       <c r="R8" t="n">
-        <v>7087946</v>
+        <v>7087945</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,11 +1393,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,7 +1419,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120168839</v>
+        <v>120168841</v>
       </c>
       <c r="B9" t="n">
         <v>57320</v>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>512725</v>
+        <v>512591</v>
       </c>
       <c r="R9" t="n">
-        <v>7087919</v>
+        <v>7087881</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack ganska färska</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,7 +1526,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120168840</v>
+        <v>120168834</v>
       </c>
       <c r="B10" t="n">
         <v>57320</v>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>512707</v>
+        <v>512698</v>
       </c>
       <c r="R10" t="n">
-        <v>7087909</v>
+        <v>7087939</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120168836</v>
+        <v>120168813</v>
       </c>
       <c r="B11" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1649,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>512738</v>
+        <v>512641</v>
       </c>
       <c r="R11" t="n">
-        <v>7087943</v>
+        <v>7087947</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,11 +1709,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1740,7 +1735,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120168842</v>
+        <v>120168840</v>
       </c>
       <c r="B12" t="n">
         <v>57320</v>
@@ -1780,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>512537</v>
+        <v>512707</v>
       </c>
       <c r="R12" t="n">
-        <v>7087781</v>
+        <v>7087909</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1820,7 +1815,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1847,10 +1842,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120168847</v>
+        <v>120168842</v>
       </c>
       <c r="B13" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1863,21 +1858,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>512728</v>
+        <v>512537</v>
       </c>
       <c r="R13" t="n">
-        <v>7087945</v>
+        <v>7087781</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1923,6 +1918,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120168834</v>
+        <v>120168844</v>
       </c>
       <c r="B14" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1965,16 +1965,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>512698</v>
+        <v>512743</v>
       </c>
       <c r="R14" t="n">
-        <v>7087939</v>
+        <v>7087946</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 58197-2023 artfynd.xlsx
+++ b/artfynd/A 58197-2023 artfynd.xlsx
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120168837</v>
+        <v>120168835</v>
       </c>
       <c r="B6" t="n">
         <v>57320</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>512736</v>
+        <v>512748</v>
       </c>
       <c r="R6" t="n">
-        <v>7087924</v>
+        <v>7087939</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120168835</v>
+        <v>120168837</v>
       </c>
       <c r="B7" t="n">
         <v>57320</v>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>512748</v>
+        <v>512736</v>
       </c>
       <c r="R7" t="n">
-        <v>7087939</v>
+        <v>7087924</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 58197-2023 artfynd.xlsx
+++ b/artfynd/A 58197-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120168845</v>
+        <v>120168836</v>
       </c>
       <c r="B2" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>512559</v>
+        <v>512738</v>
       </c>
       <c r="R2" t="n">
-        <v>7087832</v>
+        <v>7087943</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120168839</v>
+        <v>120168835</v>
       </c>
       <c r="B3" t="n">
         <v>57320</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>512725</v>
+        <v>512748</v>
       </c>
       <c r="R3" t="n">
-        <v>7087919</v>
+        <v>7087939</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120168836</v>
+        <v>120168844</v>
       </c>
       <c r="B4" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,16 +905,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512738</v>
+        <v>512743</v>
       </c>
       <c r="R4" t="n">
-        <v>7087943</v>
+        <v>7087946</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120168838</v>
+        <v>120168847</v>
       </c>
       <c r="B5" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>512730</v>
+        <v>512728</v>
       </c>
       <c r="R5" t="n">
-        <v>7087928</v>
+        <v>7087945</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,11 +1072,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120168835</v>
+        <v>120168841</v>
       </c>
       <c r="B6" t="n">
         <v>57320</v>
@@ -1143,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>512748</v>
+        <v>512591</v>
       </c>
       <c r="R6" t="n">
-        <v>7087939</v>
+        <v>7087881</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack ganska färska</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120168837</v>
+        <v>120168839</v>
       </c>
       <c r="B7" t="n">
         <v>57320</v>
@@ -1250,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>512736</v>
+        <v>512725</v>
       </c>
       <c r="R7" t="n">
-        <v>7087924</v>
+        <v>7087919</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120168847</v>
+        <v>120168838</v>
       </c>
       <c r="B8" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1357,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>512728</v>
+        <v>512730</v>
       </c>
       <c r="R8" t="n">
-        <v>7087945</v>
+        <v>7087928</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1393,6 +1388,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120168841</v>
+        <v>120168845</v>
       </c>
       <c r="B9" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1435,16 +1435,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>512591</v>
+        <v>512559</v>
       </c>
       <c r="R9" t="n">
-        <v>7087881</v>
+        <v>7087832</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack ganska färska</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,7 +1526,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120168834</v>
+        <v>120168837</v>
       </c>
       <c r="B10" t="n">
         <v>57320</v>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>512698</v>
+        <v>512736</v>
       </c>
       <c r="R10" t="n">
-        <v>7087939</v>
+        <v>7087924</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120168813</v>
+        <v>120168840</v>
       </c>
       <c r="B11" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1649,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>512641</v>
+        <v>512707</v>
       </c>
       <c r="R11" t="n">
-        <v>7087947</v>
+        <v>7087909</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,6 +1709,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,7 +1740,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120168840</v>
+        <v>120168834</v>
       </c>
       <c r="B12" t="n">
         <v>57320</v>
@@ -1775,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>512707</v>
+        <v>512698</v>
       </c>
       <c r="R12" t="n">
-        <v>7087909</v>
+        <v>7087939</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1820,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1949,10 +1954,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120168844</v>
+        <v>120168813</v>
       </c>
       <c r="B14" t="n">
-        <v>57336</v>
+        <v>90580</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1965,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1989,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>512743</v>
+        <v>512641</v>
       </c>
       <c r="R14" t="n">
-        <v>7087946</v>
+        <v>7087947</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2025,11 +2030,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 58197-2023 artfynd.xlsx
+++ b/artfynd/A 58197-2023 artfynd.xlsx
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120168835</v>
+        <v>120168839</v>
       </c>
       <c r="B3" t="n">
         <v>57320</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>512748</v>
+        <v>512725</v>
       </c>
       <c r="R3" t="n">
-        <v>7087939</v>
+        <v>7087919</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120168844</v>
+        <v>120168834</v>
       </c>
       <c r="B4" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,16 +905,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512743</v>
+        <v>512698</v>
       </c>
       <c r="R4" t="n">
-        <v>7087946</v>
+        <v>7087939</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120168847</v>
+        <v>120168838</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>512728</v>
+        <v>512730</v>
       </c>
       <c r="R5" t="n">
-        <v>7087945</v>
+        <v>7087928</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,6 +1072,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120168841</v>
+        <v>120168840</v>
       </c>
       <c r="B6" t="n">
         <v>57320</v>
@@ -1138,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>512591</v>
+        <v>512707</v>
       </c>
       <c r="R6" t="n">
-        <v>7087881</v>
+        <v>7087909</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack ganska färska</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120168839</v>
+        <v>120168813</v>
       </c>
       <c r="B7" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>512725</v>
+        <v>512641</v>
       </c>
       <c r="R7" t="n">
-        <v>7087919</v>
+        <v>7087947</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,11 +1286,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120168838</v>
+        <v>120168837</v>
       </c>
       <c r="B8" t="n">
         <v>57320</v>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>512730</v>
+        <v>512736</v>
       </c>
       <c r="R8" t="n">
-        <v>7087928</v>
+        <v>7087924</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120168845</v>
+        <v>120168847</v>
       </c>
       <c r="B9" t="n">
-        <v>57336</v>
+        <v>78542</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1435,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>512559</v>
+        <v>512728</v>
       </c>
       <c r="R9" t="n">
-        <v>7087832</v>
+        <v>7087945</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,11 +1495,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120168837</v>
+        <v>120168845</v>
       </c>
       <c r="B10" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1542,16 +1537,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1566,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>512736</v>
+        <v>512559</v>
       </c>
       <c r="R10" t="n">
-        <v>7087924</v>
+        <v>7087832</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,7 +1601,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120168840</v>
+        <v>120168844</v>
       </c>
       <c r="B11" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1649,16 +1644,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1673,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>512707</v>
+        <v>512743</v>
       </c>
       <c r="R11" t="n">
-        <v>7087909</v>
+        <v>7087946</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1713,7 +1708,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1740,7 +1735,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120168834</v>
+        <v>120168841</v>
       </c>
       <c r="B12" t="n">
         <v>57320</v>
@@ -1780,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>512698</v>
+        <v>512591</v>
       </c>
       <c r="R12" t="n">
-        <v>7087939</v>
+        <v>7087881</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1820,7 +1815,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack ganska färska</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1847,7 +1842,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120168842</v>
+        <v>120168835</v>
       </c>
       <c r="B13" t="n">
         <v>57320</v>
@@ -1887,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>512537</v>
+        <v>512748</v>
       </c>
       <c r="R13" t="n">
-        <v>7087781</v>
+        <v>7087939</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1927,7 +1922,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1954,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120168813</v>
+        <v>120168842</v>
       </c>
       <c r="B14" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1970,21 +1965,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>512641</v>
+        <v>512537</v>
       </c>
       <c r="R14" t="n">
-        <v>7087947</v>
+        <v>7087781</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2030,6 +2025,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 58197-2023 artfynd.xlsx
+++ b/artfynd/A 58197-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120168836</v>
+        <v>120168844</v>
       </c>
       <c r="B2" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>512738</v>
+        <v>512743</v>
       </c>
       <c r="R2" t="n">
-        <v>7087943</v>
+        <v>7087946</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120168839</v>
+        <v>120168813</v>
       </c>
       <c r="B3" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>512725</v>
+        <v>512641</v>
       </c>
       <c r="R3" t="n">
-        <v>7087919</v>
+        <v>7087947</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120168834</v>
+        <v>120168840</v>
       </c>
       <c r="B4" t="n">
         <v>57320</v>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512698</v>
+        <v>512707</v>
       </c>
       <c r="R4" t="n">
-        <v>7087939</v>
+        <v>7087909</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +964,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120168838</v>
+        <v>120168842</v>
       </c>
       <c r="B5" t="n">
         <v>57320</v>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>512730</v>
+        <v>512537</v>
       </c>
       <c r="R5" t="n">
-        <v>7087928</v>
+        <v>7087781</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1071,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120168840</v>
+        <v>120168845</v>
       </c>
       <c r="B6" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,16 +1114,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1143,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>512707</v>
+        <v>512559</v>
       </c>
       <c r="R6" t="n">
-        <v>7087909</v>
+        <v>7087832</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120168813</v>
+        <v>120168835</v>
       </c>
       <c r="B7" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>512641</v>
+        <v>512748</v>
       </c>
       <c r="R7" t="n">
-        <v>7087947</v>
+        <v>7087939</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,6 +1281,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120168837</v>
+        <v>120168838</v>
       </c>
       <c r="B8" t="n">
         <v>57320</v>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>512736</v>
+        <v>512730</v>
       </c>
       <c r="R8" t="n">
-        <v>7087924</v>
+        <v>7087928</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120168847</v>
+        <v>120168841</v>
       </c>
       <c r="B9" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1435,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>512728</v>
+        <v>512591</v>
       </c>
       <c r="R9" t="n">
-        <v>7087945</v>
+        <v>7087881</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,6 +1495,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack ganska färska</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120168845</v>
+        <v>120168834</v>
       </c>
       <c r="B10" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,16 +1542,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1561,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>512559</v>
+        <v>512698</v>
       </c>
       <c r="R10" t="n">
-        <v>7087832</v>
+        <v>7087939</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1606,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120168844</v>
+        <v>120168847</v>
       </c>
       <c r="B11" t="n">
-        <v>57336</v>
+        <v>78542</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1644,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1668,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>512743</v>
+        <v>512728</v>
       </c>
       <c r="R11" t="n">
-        <v>7087946</v>
+        <v>7087945</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1704,11 +1709,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,7 +1735,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120168841</v>
+        <v>120168836</v>
       </c>
       <c r="B12" t="n">
         <v>57320</v>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>512591</v>
+        <v>512738</v>
       </c>
       <c r="R12" t="n">
-        <v>7087881</v>
+        <v>7087943</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack ganska färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1842,7 +1842,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120168835</v>
+        <v>120168837</v>
       </c>
       <c r="B13" t="n">
         <v>57320</v>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>512748</v>
+        <v>512736</v>
       </c>
       <c r="R13" t="n">
-        <v>7087939</v>
+        <v>7087924</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,7 +1949,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120168842</v>
+        <v>120168839</v>
       </c>
       <c r="B14" t="n">
         <v>57320</v>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>512537</v>
+        <v>512725</v>
       </c>
       <c r="R14" t="n">
-        <v>7087781</v>
+        <v>7087919</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 58197-2023 artfynd.xlsx
+++ b/artfynd/A 58197-2023 artfynd.xlsx
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120168845</v>
+        <v>120168835</v>
       </c>
       <c r="B6" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,16 +1114,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>512559</v>
+        <v>512748</v>
       </c>
       <c r="R6" t="n">
-        <v>7087832</v>
+        <v>7087939</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120168835</v>
+        <v>120168845</v>
       </c>
       <c r="B7" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,16 +1221,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>512748</v>
+        <v>512559</v>
       </c>
       <c r="R7" t="n">
-        <v>7087939</v>
+        <v>7087832</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 58197-2023 artfynd.xlsx
+++ b/artfynd/A 58197-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120168844</v>
+        <v>120168813</v>
       </c>
       <c r="B2" t="n">
-        <v>57336</v>
+        <v>90580</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>512743</v>
+        <v>512641</v>
       </c>
       <c r="R2" t="n">
-        <v>7087946</v>
+        <v>7087947</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120168813</v>
+        <v>120168837</v>
       </c>
       <c r="B3" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>512641</v>
+        <v>512736</v>
       </c>
       <c r="R3" t="n">
-        <v>7087947</v>
+        <v>7087924</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120168840</v>
+        <v>120168835</v>
       </c>
       <c r="B4" t="n">
         <v>57320</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512707</v>
+        <v>512748</v>
       </c>
       <c r="R4" t="n">
-        <v>7087909</v>
+        <v>7087939</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120168842</v>
+        <v>120168841</v>
       </c>
       <c r="B5" t="n">
         <v>57320</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>512537</v>
+        <v>512591</v>
       </c>
       <c r="R5" t="n">
-        <v>7087781</v>
+        <v>7087881</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack ganska färska</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120168835</v>
+        <v>120168845</v>
       </c>
       <c r="B6" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,16 +1114,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>512748</v>
+        <v>512559</v>
       </c>
       <c r="R6" t="n">
-        <v>7087939</v>
+        <v>7087832</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120168845</v>
+        <v>120168834</v>
       </c>
       <c r="B7" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,16 +1221,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>512559</v>
+        <v>512698</v>
       </c>
       <c r="R7" t="n">
-        <v>7087832</v>
+        <v>7087939</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120168838</v>
+        <v>120168840</v>
       </c>
       <c r="B8" t="n">
         <v>57320</v>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>512730</v>
+        <v>512707</v>
       </c>
       <c r="R8" t="n">
-        <v>7087928</v>
+        <v>7087909</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,7 +1419,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120168841</v>
+        <v>120168842</v>
       </c>
       <c r="B9" t="n">
         <v>57320</v>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>512591</v>
+        <v>512537</v>
       </c>
       <c r="R9" t="n">
-        <v>7087881</v>
+        <v>7087781</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack ganska färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,7 +1526,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120168834</v>
+        <v>120168836</v>
       </c>
       <c r="B10" t="n">
         <v>57320</v>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>512698</v>
+        <v>512738</v>
       </c>
       <c r="R10" t="n">
-        <v>7087939</v>
+        <v>7087943</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120168847</v>
+        <v>120168839</v>
       </c>
       <c r="B11" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1649,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>512728</v>
+        <v>512725</v>
       </c>
       <c r="R11" t="n">
-        <v>7087945</v>
+        <v>7087919</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,6 +1709,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,7 +1740,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120168836</v>
+        <v>120168838</v>
       </c>
       <c r="B12" t="n">
         <v>57320</v>
@@ -1775,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>512738</v>
+        <v>512730</v>
       </c>
       <c r="R12" t="n">
-        <v>7087943</v>
+        <v>7087928</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1842,10 +1847,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120168837</v>
+        <v>120168847</v>
       </c>
       <c r="B13" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1858,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1882,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>512736</v>
+        <v>512728</v>
       </c>
       <c r="R13" t="n">
-        <v>7087924</v>
+        <v>7087945</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1918,11 +1923,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120168839</v>
+        <v>120168844</v>
       </c>
       <c r="B14" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1965,16 +1965,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>512725</v>
+        <v>512743</v>
       </c>
       <c r="R14" t="n">
-        <v>7087919</v>
+        <v>7087946</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 58197-2023 artfynd.xlsx
+++ b/artfynd/A 58197-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120168813</v>
+        <v>120168845</v>
       </c>
       <c r="B2" t="n">
-        <v>90580</v>
+        <v>57336</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>512641</v>
+        <v>512559</v>
       </c>
       <c r="R2" t="n">
-        <v>7087947</v>
+        <v>7087832</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120168837</v>
+        <v>120168838</v>
       </c>
       <c r="B3" t="n">
         <v>57320</v>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>512736</v>
+        <v>512730</v>
       </c>
       <c r="R3" t="n">
-        <v>7087924</v>
+        <v>7087928</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120168835</v>
+        <v>120168841</v>
       </c>
       <c r="B4" t="n">
         <v>57320</v>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512748</v>
+        <v>512591</v>
       </c>
       <c r="R4" t="n">
-        <v>7087939</v>
+        <v>7087881</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack ganska färska</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120168841</v>
+        <v>120168839</v>
       </c>
       <c r="B5" t="n">
         <v>57320</v>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>512591</v>
+        <v>512725</v>
       </c>
       <c r="R5" t="n">
-        <v>7087881</v>
+        <v>7087919</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack ganska färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120168845</v>
+        <v>120168837</v>
       </c>
       <c r="B6" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,16 +1119,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1138,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>512559</v>
+        <v>512736</v>
       </c>
       <c r="R6" t="n">
-        <v>7087832</v>
+        <v>7087924</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120168834</v>
+        <v>120168840</v>
       </c>
       <c r="B7" t="n">
         <v>57320</v>
@@ -1245,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>512698</v>
+        <v>512707</v>
       </c>
       <c r="R7" t="n">
-        <v>7087939</v>
+        <v>7087909</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120168840</v>
+        <v>120168836</v>
       </c>
       <c r="B8" t="n">
         <v>57320</v>
@@ -1352,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>512707</v>
+        <v>512738</v>
       </c>
       <c r="R8" t="n">
-        <v>7087909</v>
+        <v>7087943</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1397,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120168842</v>
+        <v>120168847</v>
       </c>
       <c r="B9" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1435,21 +1440,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>512537</v>
+        <v>512728</v>
       </c>
       <c r="R9" t="n">
-        <v>7087781</v>
+        <v>7087945</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,11 +1500,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120168836</v>
+        <v>120168844</v>
       </c>
       <c r="B10" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1542,16 +1542,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>512738</v>
+        <v>512743</v>
       </c>
       <c r="R10" t="n">
-        <v>7087943</v>
+        <v>7087946</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120168839</v>
+        <v>120168813</v>
       </c>
       <c r="B11" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1649,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>512725</v>
+        <v>512641</v>
       </c>
       <c r="R11" t="n">
-        <v>7087919</v>
+        <v>7087947</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,11 +1709,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1740,7 +1735,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120168838</v>
+        <v>120168834</v>
       </c>
       <c r="B12" t="n">
         <v>57320</v>
@@ -1780,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>512730</v>
+        <v>512698</v>
       </c>
       <c r="R12" t="n">
-        <v>7087928</v>
+        <v>7087939</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1820,7 +1815,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1847,10 +1842,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120168847</v>
+        <v>120168842</v>
       </c>
       <c r="B13" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1863,21 +1858,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>512728</v>
+        <v>512537</v>
       </c>
       <c r="R13" t="n">
-        <v>7087945</v>
+        <v>7087781</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1923,6 +1918,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120168844</v>
+        <v>120168835</v>
       </c>
       <c r="B14" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1965,16 +1965,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>512743</v>
+        <v>512748</v>
       </c>
       <c r="R14" t="n">
-        <v>7087946</v>
+        <v>7087939</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 58197-2023 artfynd.xlsx
+++ b/artfynd/A 58197-2023 artfynd.xlsx
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120168836</v>
+        <v>120168847</v>
       </c>
       <c r="B8" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,21 +1333,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>512738</v>
+        <v>512728</v>
       </c>
       <c r="R8" t="n">
-        <v>7087943</v>
+        <v>7087945</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1393,11 +1393,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120168847</v>
+        <v>120168844</v>
       </c>
       <c r="B9" t="n">
-        <v>78542</v>
+        <v>57336</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1440,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>512728</v>
+        <v>512743</v>
       </c>
       <c r="R9" t="n">
-        <v>7087945</v>
+        <v>7087946</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1500,6 +1495,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120168844</v>
+        <v>120168836</v>
       </c>
       <c r="B10" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1542,16 +1542,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>512743</v>
+        <v>512738</v>
       </c>
       <c r="R10" t="n">
-        <v>7087946</v>
+        <v>7087943</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
